--- a/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPJ_DAE_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPJ_DAE_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DAE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="ADVERTENCIAS_ESPERADAS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DAE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADVERTENCIAS_ESPERADAS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPJ_DAE_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_con_advertencias/MPJ_DAE_2026_T1_Chaco_CON_ADVERTENCIAS.xlsx
@@ -270,7 +270,7 @@
         <t>ID del Niño, niña o Adolescente
 Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -626,7 +626,7 @@
       <text>
         <t>ID del Niño, niña o Adolescente
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -1326,9 +1326,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>42.84</v>
       </c>
       <c r="AI4" s="5" t="n">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>29.65</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>87.76000000000001</v>
       </c>
       <c r="AI6" s="5" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>45590</v>
+        <v>45591</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>38.78</v>
       </c>
       <c r="AI7" s="5" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>33.09</v>
       </c>
       <c r="AI8" s="5" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45940</v>
+        <v>45941</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>59.26</v>
       </c>
       <c r="AI9" s="5" t="n">
-        <v>45942</v>
+        <v>45943</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>86.52</v>
       </c>
       <c r="AI10" s="5" t="n">
-        <v>45859</v>
+        <v>45860</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>1.21</v>
       </c>
       <c r="AI11" s="5" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>45609</v>
+        <v>45610</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45595</v>
+        <v>45596</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>25.38</v>
       </c>
       <c r="AI12" s="5" t="n">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="AK12" s="13" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="AL12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>44.38</v>
       </c>
       <c r="AI13" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>45745</v>
+        <v>45746</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>34.02</v>
       </c>
       <c r="AI14" s="5" t="n">
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>75.2</v>
       </c>
       <c r="AI15" s="5" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>51.43</v>
       </c>
       <c r="AI16" s="5" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>66.68000000000001</v>
       </c>
       <c r="AI17" s="5" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>45984</v>
+        <v>45985</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>79.58</v>
       </c>
       <c r="AI18" s="5" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="AL18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>18.41</v>
       </c>
       <c r="AI19" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45716</v>
+        <v>45717</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>71.64</v>
       </c>
       <c r="AI20" s="5" t="n">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>60.72</v>
       </c>
       <c r="AI21" s="5" t="n">
-        <v>45792</v>
+        <v>45793</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>45840</v>
+        <v>45841</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>33.36</v>
       </c>
       <c r="AI22" s="5" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>61.12</v>
       </c>
       <c r="AI23" s="5" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45785</v>
+        <v>45786</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>89.27</v>
       </c>
       <c r="AI24" s="5" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>45752</v>
+        <v>45753</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>88.15000000000001</v>
       </c>
       <c r="AI25" s="5" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>45757</v>
+        <v>45758</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>35.83</v>
       </c>
       <c r="AI26" s="5" t="n">
-        <v>45860</v>
+        <v>45861</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>2.21</v>
       </c>
       <c r="AI27" s="5" t="n">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45982</v>
+        <v>45983</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>62.48</v>
       </c>
       <c r="AI28" s="5" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>54.91</v>
       </c>
       <c r="AI29" s="5" t="n">
-        <v>45849</v>
+        <v>45850</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>45696</v>
+        <v>45697</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>65.5</v>
       </c>
       <c r="AI30" s="5" t="n">
-        <v>45768</v>
+        <v>45769</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>45873</v>
+        <v>45874</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>41.91</v>
       </c>
       <c r="AI31" s="5" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45776</v>
+        <v>45777</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>93.33</v>
       </c>
       <c r="AI32" s="5" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>76.52</v>
       </c>
       <c r="AI33" s="5" t="n">
-        <v>45832</v>
+        <v>45833</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="AK33" s="13" t="n">
-        <v>46633</v>
+        <v>46634</v>
       </c>
       <c r="AL33" t="inlineStr"/>
     </row>
@@ -8131,9 +8131,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -8319,7 +8319,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>45806</v>
+        <v>45807</v>
       </c>
       <c r="AD4" s="8" t="n">
         <v>0.6041666666666666</v>
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="AJ4" s="5" t="n">
-        <v>45904</v>
+        <v>45905</v>
       </c>
       <c r="AK4" s="8" t="n">
         <v>0.6979166666666666</v>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>45707</v>
+        <v>45708</v>
       </c>
       <c r="AD5" s="8" t="n">
         <v>0.46875</v>
@@ -8664,7 +8664,7 @@
         </is>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>45882</v>
+        <v>45883</v>
       </c>
       <c r="AK5" s="8" t="n">
         <v>0.5729166666666666</v>
@@ -8692,7 +8692,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>45984</v>
+        <v>45985</v>
       </c>
       <c r="AD6" s="8" t="n">
         <v>0.625</v>
@@ -8846,7 +8846,7 @@
         </is>
       </c>
       <c r="AJ6" s="5" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="AK6" s="8" t="n">
         <v>0.3229166666666667</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="AM6" s="13" t="n">
-        <v>46649</v>
+        <v>46650</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>45940</v>
+        <v>45941</v>
       </c>
       <c r="AD7" s="8" t="n">
         <v>0.40625</v>
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="AK7" s="8" t="n">
         <v>0.7708333333333334</v>
@@ -9058,7 +9058,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>45821</v>
+        <v>45822</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="AD8" s="8" t="n">
         <v>0.4166666666666667</v>
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="AJ8" s="5" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="AK8" s="8" t="n">
         <v>0.96875</v>
@@ -9248,7 +9248,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>45616</v>
+        <v>45617</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="N9" s="5" t="n">
-        <v>46579</v>
+        <v>46580</v>
       </c>
       <c r="O9" s="6" t="n">
         <v>11</v>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="AD9" s="8" t="n">
         <v>0.3125</v>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="AJ9" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK9" s="8" t="n">
         <v>0.96875</v>
@@ -9429,7 +9429,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>45610</v>
+        <v>45611</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45824</v>
+        <v>45825</v>
       </c>
       <c r="AD10" s="8" t="n">
         <v>0.9270833333333334</v>
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="AJ10" s="5" t="n">
-        <v>45840</v>
+        <v>45841</v>
       </c>
       <c r="AK10" s="8" t="n">
         <v>0.90625</v>
@@ -9615,7 +9615,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="AD11" s="8" t="n">
         <v>0.84375</v>
@@ -9773,7 +9773,7 @@
         </is>
       </c>
       <c r="AJ11" s="5" t="n">
-        <v>46033</v>
+        <v>46034</v>
       </c>
       <c r="AK11" s="8" t="n">
         <v>0.3958333333333333</v>
@@ -9801,7 +9801,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="AD12" s="8" t="n">
-        <v>46629</v>
+        <v>46630</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         </is>
       </c>
       <c r="AJ12" s="5" t="n">
-        <v>45772</v>
+        <v>45773</v>
       </c>
       <c r="AK12" s="8" t="n">
         <v>0.9583333333333334</v>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="AM12" s="13" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="AD13" s="8" t="n">
         <v>0.4583333333333333</v>
@@ -10157,7 +10157,7 @@
         </is>
       </c>
       <c r="AJ13" s="5" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="AK13" s="8" t="n">
         <v>0.8645833333333334</v>
@@ -10185,7 +10185,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="AD14" s="8" t="n">
         <v>0.9375</v>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="AJ14" s="5" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="AK14" s="8" t="n">
         <v>0.3541666666666667</v>
@@ -10380,7 +10380,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>45872</v>
+        <v>45873</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="AD15" s="8" t="n">
         <v>0.9270833333333334</v>
@@ -10539,7 +10539,7 @@
         </is>
       </c>
       <c r="AJ15" s="5" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="AK15" s="8" t="n">
         <v>0.59375</v>
@@ -10575,7 +10575,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>45781</v>
+        <v>45782</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="AD16" s="8" t="n">
         <v>0.7291666666666666</v>
@@ -10729,7 +10729,7 @@
         </is>
       </c>
       <c r="AJ16" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK16" s="8" t="n">
         <v>0.8333333333333334</v>
@@ -10765,7 +10765,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45591</v>
+        <v>45592</v>
       </c>
       <c r="AD17" s="8" t="n">
         <v>0.3125</v>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="AJ17" s="5" t="n">
-        <v>45690</v>
+        <v>45691</v>
       </c>
       <c r="AK17" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -10956,7 +10956,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>45969</v>
+        <v>45970</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="AD18" s="8" t="n">
         <v>0.5520833333333334</v>
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK18" s="8" t="n">
         <v>0.9583333333333334</v>
@@ -11142,7 +11142,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>45814</v>
+        <v>45815</v>
       </c>
       <c r="AD19" s="8" t="n">
         <v>0.65625</v>
@@ -11296,7 +11296,7 @@
         </is>
       </c>
       <c r="AJ19" s="5" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="AK19" s="8" t="n">
         <v>0.3229166666666667</v>
@@ -11328,7 +11328,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="AD20" s="8" t="n">
         <v>0.3958333333333333</v>
@@ -11487,7 +11487,7 @@
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="AK20" s="8" t="n">
         <v>0.4479166666666667</v>
@@ -11519,7 +11519,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="N21" s="5" t="n">
-        <v>46515</v>
+        <v>46516</v>
       </c>
       <c r="O21" s="6" t="n">
         <v>13</v>
@@ -11651,7 +11651,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="AD21" s="8" t="n">
         <v>0.7083333333333334</v>
@@ -11682,7 +11682,7 @@
         </is>
       </c>
       <c r="AJ21" s="5" t="n">
-        <v>45850</v>
+        <v>45851</v>
       </c>
       <c r="AK21" s="8" t="n">
         <v>0.7291666666666666</v>
@@ -11714,7 +11714,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="AD22" s="8" t="n">
         <v>0.6875</v>
@@ -11868,7 +11868,7 @@
         </is>
       </c>
       <c r="AJ22" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK22" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -11900,7 +11900,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>45839</v>
+        <v>45840</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45610</v>
+        <v>45611</v>
       </c>
       <c r="AD23" s="8" t="n">
         <v>0.6458333333333334</v>
@@ -12054,7 +12054,7 @@
         </is>
       </c>
       <c r="AJ23" s="5" t="n">
-        <v>45700</v>
+        <v>45701</v>
       </c>
       <c r="AK23" s="8" t="n">
         <v>0.8333333333333334</v>
@@ -12086,7 +12086,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>45634</v>
+        <v>45635</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45832</v>
+        <v>45833</v>
       </c>
       <c r="AD24" s="8" t="n">
         <v>0.34375</v>
@@ -12249,7 +12249,7 @@
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
-        <v>45896</v>
+        <v>45897</v>
       </c>
       <c r="AK24" s="8" t="n">
         <v>0.375</v>
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="AM24" s="13" t="n">
-        <v>46630</v>
+        <v>46631</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="AD25" s="8" t="n">
         <v>0.71875</v>
@@ -12446,7 +12446,7 @@
         </is>
       </c>
       <c r="AJ25" s="5" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="AK25" s="8" t="n">
         <v>0.7291666666666666</v>
@@ -12478,7 +12478,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45843</v>
+        <v>45844</v>
       </c>
       <c r="AD26" s="8" t="n">
         <v>0.9166666666666666</v>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="AJ26" s="5" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="AK26" s="8" t="n">
         <v>0.5625</v>
@@ -12673,7 +12673,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         </is>
       </c>
       <c r="N27" s="5" t="n">
-        <v>46399</v>
+        <v>46400</v>
       </c>
       <c r="O27" s="6" t="n">
         <v>3</v>
@@ -12800,7 +12800,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>45792</v>
+        <v>45793</v>
       </c>
       <c r="AD27" s="8" t="n">
         <v>0.5729166666666666</v>
@@ -12831,7 +12831,7 @@
         </is>
       </c>
       <c r="AJ27" s="5" t="n">
-        <v>45833</v>
+        <v>45834</v>
       </c>
       <c r="AK27" s="8" t="n">
         <v>0.8645833333333334</v>
@@ -12859,7 +12859,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="AD28" s="8" t="n">
         <v>0.6770833333333334</v>
@@ -13022,7 +13022,7 @@
         </is>
       </c>
       <c r="AJ28" s="5" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="AK28" s="8" t="n">
         <v>0.875</v>
@@ -13050,7 +13050,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>45689</v>
+        <v>45690</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="AD29" s="8" t="n">
         <v>0.7291666666666666</v>
@@ -13209,7 +13209,7 @@
         </is>
       </c>
       <c r="AJ29" s="5" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="AK29" s="8" t="n">
         <v>0.3854166666666667</v>
@@ -13237,7 +13237,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>45670</v>
+        <v>45671</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>45597</v>
+        <v>45598</v>
       </c>
       <c r="AD30" s="8" t="n">
         <v>0.40625</v>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="AJ30" s="5" t="n">
-        <v>45765</v>
+        <v>45766</v>
       </c>
       <c r="AK30" s="8" t="n">
         <v>0.5416666666666666</v>
@@ -13427,7 +13427,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>46074</v>
+        <v>46075</v>
       </c>
       <c r="AD31" s="8" t="n">
         <v>0.9791666666666666</v>
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="AJ31" s="5" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="AK31" s="8" t="n">
         <v>0.6875</v>
@@ -13617,7 +13617,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="AD32" s="8" t="n">
         <v>0.7395833333333334</v>
@@ -13771,7 +13771,7 @@
         </is>
       </c>
       <c r="AJ32" s="5" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="AK32" s="8" t="n">
         <v>0.9791666666666666</v>
@@ -13799,7 +13799,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="AD33" s="8" t="n">
         <v>0.5416666666666666</v>
@@ -13953,7 +13953,7 @@
         </is>
       </c>
       <c r="AJ33" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AK33" s="8" t="n">
         <v>0.4791666666666667</v>
@@ -13964,7 +13964,7 @@
         </is>
       </c>
       <c r="AM33" s="13" t="n">
-        <v>46641</v>
+        <v>46642</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
@@ -16062,7 +16062,8 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.</t>
+          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
+Campo obligatorio.</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16568,11 @@
           <t>ID del Niño, niña o Adolescente</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Campo obligatorio.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
